--- a/excel_reports/attendance_report.xlsx
+++ b/excel_reports/attendance_report.xlsx
@@ -428,11 +428,11 @@
   <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -440,39 +440,35 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Employee ID</t>
+          <t>Employee IDEmployee Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>Join Date</t>
         </is>
       </c>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
